--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N100_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N100_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.624549969149587</v>
+        <v>1.563989369986808</v>
       </c>
       <c r="D2" t="n">
-        <v>20.25790502617145</v>
+        <v>3.291909566752861</v>
       </c>
       <c r="E2" t="n">
-        <v>22.37915248805941</v>
+        <v>3.636612279309654</v>
       </c>
       <c r="F2" t="n">
-        <v>17.41398584260283</v>
+        <v>2.82977269942296</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>62.91110411078062</v>
+        <v>10.22305441800185</v>
       </c>
       <c r="D3" t="n">
-        <v>59.74322831010647</v>
+        <v>9.708274600392301</v>
       </c>
       <c r="E3" t="n">
-        <v>22.37915248805941</v>
+        <v>3.636612279309654</v>
       </c>
       <c r="F3" t="n">
-        <v>17.41398584260283</v>
+        <v>2.82977269942296</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.12662162221793</v>
+        <v>4.083076013610413</v>
       </c>
       <c r="D4" t="n">
-        <v>26.02583958525724</v>
+        <v>4.229198932604302</v>
       </c>
       <c r="E4" t="n">
-        <v>22.37915248805941</v>
+        <v>3.636612279309654</v>
       </c>
       <c r="F4" t="n">
-        <v>17.41398584260283</v>
+        <v>2.82977269942296</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
